--- a/docs/harness/wirelist/CAN-wirelist.xlsx
+++ b/docs/harness/wirelist/CAN-wirelist.xlsx
@@ -1212,12 +1212,12 @@
       <c r="AD3" s="38" t="inlineStr"/>
       <c r="AE3" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_com C3 CAN 1 High (CAN1H)</t>
+          <t>channels.csv ecu_com C3 CAN 1 High (CAN1H); splice sp_canh: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canh is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG3" s="38" t="inlineStr"/>
@@ -1329,12 +1329,12 @@
       <c r="AD4" s="54" t="inlineStr"/>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_com C4 CAN 1 Low (CAN1L)</t>
+          <t>channels.csv ecu_com C4 CAN 1 Low (CAN1L); splice sp_canl: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canl is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG4" s="54" t="inlineStr"/>
@@ -1440,7 +1440,7 @@
       <c r="AD5" s="38" t="inlineStr"/>
       <c r="AE5" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_can named in SoT</t>
+          <t>splice sp_shield_can: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF5" s="38" t="inlineStr">
@@ -1553,10 +1553,14 @@
       <c r="AB6" s="53" t="inlineStr"/>
       <c r="AC6" s="54" t="inlineStr"/>
       <c r="AD6" s="54" t="inlineStr"/>
-      <c r="AE6" s="54" t="inlineStr"/>
+      <c r="AE6" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_canh: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF6" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canh is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG6" s="54" t="inlineStr"/>
@@ -1660,10 +1664,14 @@
       <c r="AB7" s="37" t="inlineStr"/>
       <c r="AC7" s="38" t="inlineStr"/>
       <c r="AD7" s="38" t="inlineStr"/>
-      <c r="AE7" s="38" t="inlineStr"/>
+      <c r="AE7" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_canl: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF7" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canl is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG7" s="38" t="inlineStr"/>
@@ -1767,10 +1775,14 @@
       <c r="AB8" s="53" t="inlineStr"/>
       <c r="AC8" s="54" t="inlineStr"/>
       <c r="AD8" s="54" t="inlineStr"/>
-      <c r="AE8" s="54" t="inlineStr"/>
+      <c r="AE8" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_canh_lam: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF8" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canh_lam is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG8" s="54" t="inlineStr"/>
@@ -1874,10 +1886,14 @@
       <c r="AB9" s="37" t="inlineStr"/>
       <c r="AC9" s="38" t="inlineStr"/>
       <c r="AD9" s="38" t="inlineStr"/>
-      <c r="AE9" s="38" t="inlineStr"/>
+      <c r="AE9" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_canl_lam: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF9" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canl_lam is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG9" s="38" t="inlineStr"/>
@@ -1989,10 +2005,14 @@
       <c r="AB10" s="53" t="inlineStr"/>
       <c r="AC10" s="54" t="inlineStr"/>
       <c r="AD10" s="54" t="inlineStr"/>
-      <c r="AE10" s="54" t="inlineStr"/>
+      <c r="AE10" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_canh: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF10" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canh is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG10" s="54" t="inlineStr">
@@ -2108,12 +2128,12 @@
       <c r="AD11" s="38" t="inlineStr"/>
       <c r="AE11" s="38" t="inlineStr">
         <is>
-          <t>end t_cluster_can named in SoT</t>
+          <t>splice sp_canh: node of the wire list (SoT); end t_cluster_can: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF11" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canh is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG11" s="38" t="inlineStr"/>
@@ -2223,10 +2243,14 @@
       <c r="AB12" s="53" t="inlineStr"/>
       <c r="AC12" s="54" t="inlineStr"/>
       <c r="AD12" s="54" t="inlineStr"/>
-      <c r="AE12" s="54" t="inlineStr"/>
+      <c r="AE12" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_canh: node of the wire list (SoT); end t_realdash_can: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF12" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canh is not named in the SoT (drawing only); end t_realdash_can (Pi USB-CAN adapter CANH + CANL pins (center dash)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG12" s="54" t="inlineStr"/>
@@ -2330,10 +2354,14 @@
       <c r="AB13" s="37" t="inlineStr"/>
       <c r="AC13" s="38" t="inlineStr"/>
       <c r="AD13" s="38" t="inlineStr"/>
-      <c r="AE13" s="38" t="inlineStr"/>
+      <c r="AE13" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_canh_lam: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF13" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canh_lam is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG13" s="38" t="inlineStr"/>
@@ -2445,10 +2473,14 @@
       <c r="AB14" s="53" t="inlineStr"/>
       <c r="AC14" s="54" t="inlineStr"/>
       <c r="AD14" s="54" t="inlineStr"/>
-      <c r="AE14" s="54" t="inlineStr"/>
+      <c r="AE14" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_canl: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF14" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canl is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG14" s="54" t="inlineStr">
@@ -2564,12 +2596,12 @@
       <c r="AD15" s="38" t="inlineStr"/>
       <c r="AE15" s="38" t="inlineStr">
         <is>
-          <t>end t_cluster_can named in SoT</t>
+          <t>splice sp_canl: node of the wire list (SoT); end t_cluster_can: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF15" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canl is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG15" s="38" t="inlineStr"/>
@@ -2679,10 +2711,14 @@
       <c r="AB16" s="53" t="inlineStr"/>
       <c r="AC16" s="54" t="inlineStr"/>
       <c r="AD16" s="54" t="inlineStr"/>
-      <c r="AE16" s="54" t="inlineStr"/>
+      <c r="AE16" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_canl: node of the wire list (SoT); end t_realdash_can: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF16" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canl is not named in the SoT (drawing only); end t_realdash_can (Pi USB-CAN adapter CANH + CANL pins (center dash)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG16" s="54" t="inlineStr"/>
@@ -2786,10 +2822,14 @@
       <c r="AB17" s="37" t="inlineStr"/>
       <c r="AC17" s="38" t="inlineStr"/>
       <c r="AD17" s="38" t="inlineStr"/>
-      <c r="AE17" s="38" t="inlineStr"/>
+      <c r="AE17" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_canl_lam: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF17" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canl_lam is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG17" s="38" t="inlineStr"/>
@@ -2893,12 +2933,12 @@
       <c r="AD18" s="54" t="inlineStr"/>
       <c r="AE18" s="54" t="inlineStr">
         <is>
-          <t>splice sp_dev named in SoT</t>
+          <t>splice sp_dev: node of the wire list (SoT); end t_cluster_pwr: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF18" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_cluster_pwr (Cluster buck converter IN+ pin (old meter spot)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG18" s="54" t="inlineStr"/>
@@ -3002,12 +3042,12 @@
       <c r="AD19" s="38" t="inlineStr"/>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>splice sp_dev named in SoT</t>
+          <t>splice sp_dev: node of the wire list (SoT); end t_realdash_pwr: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_realdash_pwr (Pi 12-to-5 V supply IN+ pin (center dash)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG19" s="38" t="inlineStr"/>
@@ -3113,7 +3153,7 @@
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_can named in SoT</t>
+          <t>splice sp_shield_can: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
@@ -3232,7 +3272,7 @@
       <c r="AD21" s="38" t="inlineStr"/>
       <c r="AE21" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_can named in SoT</t>
+          <t>splice sp_shield_can: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF21" s="38" t="inlineStr">
@@ -3347,7 +3387,7 @@
       <c r="AD22" s="54" t="inlineStr"/>
       <c r="AE22" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_can named in SoT</t>
+          <t>splice sp_shield_can: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF22" s="54" t="inlineStr">
@@ -3456,10 +3496,14 @@
       <c r="AB23" s="37" t="inlineStr"/>
       <c r="AC23" s="38" t="inlineStr"/>
       <c r="AD23" s="38" t="inlineStr"/>
-      <c r="AE23" s="38" t="inlineStr"/>
+      <c r="AE23" s="38" t="inlineStr">
+        <is>
+          <t>end t_cluster_gnd_lead: end row of the wire list (SoT); end t_cluster_gnd: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF23" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_cluster_gnd_lead (Cluster buck converter IN- pin (old meter spot)) is drawing-only: not named in the SoT; end t_cluster_gnd (Ground point IF, I/P brace RH (EWD ground point IF, p.42)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG23" s="38" t="inlineStr"/>
@@ -3559,10 +3603,14 @@
       <c r="AB24" s="53" t="inlineStr"/>
       <c r="AC24" s="54" t="inlineStr"/>
       <c r="AD24" s="54" t="inlineStr"/>
-      <c r="AE24" s="54" t="inlineStr"/>
+      <c r="AE24" s="54" t="inlineStr">
+        <is>
+          <t>end t_realdash_gnd_lead: end row of the wire list (SoT); end t_realdash_gnd: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF24" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_realdash_gnd_lead (Pi 12-to-5 V supply IN- pin (center dash)) is drawing-only: not named in the SoT; end t_realdash_gnd (Ground point IF, I/P brace RH (EWD ground point IF, p.42)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG24" s="54" t="inlineStr"/>
@@ -4057,7 +4105,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4161,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4217,7 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4273,7 @@
       </c>
       <c r="L6" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4329,7 @@
       </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4385,7 @@
       </c>
       <c r="L8" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/CAN-wirelist.xlsx
+++ b/docs/harness/wirelist/CAN-wirelist.xlsx
@@ -2902,7 +2902,7 @@
       </c>
       <c r="R18" s="47" t="inlineStr">
         <is>
-          <t>+12V DEV 15A (LOGIC BUS2-6)</t>
+          <t>+12V Dash devices +12 V (LOGIC BUS2-6)</t>
         </is>
       </c>
       <c r="S18" s="48" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="R19" s="31" t="inlineStr">
         <is>
-          <t>+12V DEV 15A (LOGIC BUS2-6)</t>
+          <t>+12V Dash devices +12 V (LOGIC BUS2-6)</t>
         </is>
       </c>
       <c r="S19" s="32" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="E8" s="47" t="inlineStr">
         <is>
-          <t>+12V DEV 15A (LOGIC BUS2-6)</t>
+          <t>+12V Dash devices +12 V (LOGIC BUS2-6)</t>
         </is>
       </c>
       <c r="F8" s="48" t="n">

--- a/docs/harness/wirelist/CAN-wirelist.xlsx
+++ b/docs/harness/wirelist/CAN-wirelist.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Mates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wire list'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Splices'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Connectors'!$A$2:$G$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Connectors'!$1:$2</definedName>
@@ -733,14 +733,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG28"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>cab_can_ecu_sh</t>
+          <t>w_shd_can_trunk</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -1358,23 +1358,27 @@
       <c r="D5" s="23" t="inlineStr"/>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>cable screen</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>cab_can_ecu</t>
+          <t>ecu_com</t>
         </is>
       </c>
       <c r="G5" s="26" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
-        </is>
-      </c>
-      <c r="H5" s="25" t="inlineStr"/>
+          <t>ECU COMMS</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
-          <t>ECU CAN shield</t>
+          <t>CAN screen trunk</t>
         </is>
       </c>
       <c r="J5" s="26" t="inlineStr"/>
@@ -1385,54 +1389,58 @@
       </c>
       <c r="L5" s="28" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
+          <t>sp_can_sh_clu</t>
         </is>
       </c>
       <c r="M5" s="29" t="inlineStr">
         <is>
-          <t>splice sp_shield_can (CAN screen join)</t>
+          <t>splice sp_can_sh_clu (SP-CAN-SH-CLU)</t>
         </is>
       </c>
       <c r="N5" s="28" t="inlineStr"/>
       <c r="O5" s="29" t="inlineStr">
         <is>
-          <t>ECU CAN shield</t>
+          <t>CAN screen trunk</t>
         </is>
       </c>
       <c r="P5" s="29" t="inlineStr"/>
       <c r="Q5" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="R5" s="31" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
         </is>
       </c>
       <c r="S5" s="32" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
-        </is>
-      </c>
-      <c r="T5" s="32" t="inlineStr">
-        <is>
-          <t>cab_can_ecu</t>
-        </is>
-      </c>
-      <c r="U5" s="33" t="inlineStr"/>
+          <t>sp_can_sh_clu</t>
+        </is>
+      </c>
+      <c r="T5" s="32" t="inlineStr"/>
+      <c r="U5" s="33" t="n">
+        <v>20</v>
+      </c>
       <c r="V5" s="34" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="W5" s="34" t="inlineStr"/>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W5" s="34" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
       <c r="X5" s="34" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
       </c>
-      <c r="Y5" s="34" t="inlineStr"/>
+      <c r="Y5" s="34" t="n">
+        <v>180</v>
+      </c>
       <c r="Z5" s="35" t="inlineStr"/>
       <c r="AA5" s="36" t="inlineStr"/>
       <c r="AB5" s="37" t="inlineStr"/>
@@ -1440,7 +1448,7 @@
       <c r="AD5" s="38" t="inlineStr"/>
       <c r="AE5" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_can: node of the wire list (SoT)</t>
+          <t>channels.csv ecu_com C1 Comms 1 (CAN_SCREEN); splice sp_can_sh_clu: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF5" s="38" t="inlineStr">
@@ -1450,7 +1458,7 @@
       </c>
       <c r="AG5" s="38" t="inlineStr">
         <is>
-          <t>screen floats at the far end</t>
+          <t>the trunk drain: the ONE CAN drain wire on C1; every node drain is soldered onto it (R30)</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1470,7 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>wc_term1</t>
+          <t>cab_can_ecu_sh</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
@@ -1473,72 +1481,72 @@
       <c r="D6" s="39" t="inlineStr"/>
       <c r="E6" s="40" t="inlineStr">
         <is>
-          <t>resistor</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>r_term_ecu</t>
+          <t>sp_can_sh_clu</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t>r_term_ecu</t>
-        </is>
-      </c>
-      <c r="H6" s="41" t="n">
-        <v>1</v>
-      </c>
+          <t>splice sp_can_sh_clu (SP-CAN-SH-CLU)</t>
+        </is>
+      </c>
+      <c r="H6" s="41" t="inlineStr"/>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>ECU 120R CAN H</t>
+          <t>ECU CAN shield</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr"/>
       <c r="K6" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="L6" s="44" t="inlineStr">
         <is>
-          <t>sp_canh</t>
+          <t>cab_can_ecu</t>
         </is>
       </c>
       <c r="M6" s="45" t="inlineStr">
         <is>
-          <t>splice sp_canh (CAN H join)</t>
+          <t>cable screen (one end only)</t>
         </is>
       </c>
       <c r="N6" s="44" t="inlineStr"/>
       <c r="O6" s="45" t="inlineStr">
         <is>
-          <t>ECU 120R CAN H</t>
+          <t>ECU CAN shield</t>
         </is>
       </c>
       <c r="P6" s="45" t="inlineStr"/>
       <c r="Q6" s="46" t="inlineStr">
         <is>
-          <t>ECU-COMMS.C3</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="R6" s="47" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda (ECU-COMMS C3)</t>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
         </is>
       </c>
       <c r="S6" s="48" t="inlineStr">
         <is>
-          <t>sp_canh</t>
-        </is>
-      </c>
-      <c r="T6" s="48" t="inlineStr"/>
-      <c r="U6" s="49" t="n">
-        <v>20</v>
-      </c>
+          <t>sp_can_sh_clu</t>
+        </is>
+      </c>
+      <c r="T6" s="48" t="inlineStr">
+        <is>
+          <t>cab_can_ecu</t>
+        </is>
+      </c>
+      <c r="U6" s="49" t="inlineStr"/>
       <c r="V6" s="50" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="W6" s="50" t="inlineStr"/>
@@ -1555,7 +1563,7 @@
       <c r="AD6" s="54" t="inlineStr"/>
       <c r="AE6" s="54" t="inlineStr">
         <is>
-          <t>splice sp_canh: node of the wire list (SoT)</t>
+          <t>splice sp_can_sh_clu: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF6" s="54" t="inlineStr">
@@ -1563,7 +1571,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG6" s="54" t="inlineStr"/>
+      <c r="AG6" s="54" t="inlineStr">
+        <is>
+          <t>screen floats at the far (ECU) end</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
@@ -1573,7 +1585,7 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>wc_term2</t>
+          <t>wc_term1</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -1598,11 +1610,11 @@
         </is>
       </c>
       <c r="H7" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="26" t="inlineStr">
         <is>
-          <t>ECU 120R CAN L</t>
+          <t>ECU 120R CAN H</t>
         </is>
       </c>
       <c r="J7" s="26" t="inlineStr"/>
@@ -1613,34 +1625,34 @@
       </c>
       <c r="L7" s="28" t="inlineStr">
         <is>
-          <t>sp_canl</t>
+          <t>sp_canh</t>
         </is>
       </c>
       <c r="M7" s="29" t="inlineStr">
         <is>
-          <t>splice sp_canl (CAN L join)</t>
+          <t>splice sp_canh (CAN H join)</t>
         </is>
       </c>
       <c r="N7" s="28" t="inlineStr"/>
       <c r="O7" s="29" t="inlineStr">
         <is>
-          <t>ECU 120R CAN L</t>
+          <t>ECU 120R CAN H</t>
         </is>
       </c>
       <c r="P7" s="29" t="inlineStr"/>
       <c r="Q7" s="30" t="inlineStr">
         <is>
-          <t>ECU-COMMS.C4</t>
+          <t>ECU-COMMS.C3</t>
         </is>
       </c>
       <c r="R7" s="31" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda (ECU-COMMS C4)</t>
+          <t>CAN H to CAN-Lambda (ECU-COMMS C3)</t>
         </is>
       </c>
       <c r="S7" s="32" t="inlineStr">
         <is>
-          <t>sp_canl</t>
+          <t>sp_canh</t>
         </is>
       </c>
       <c r="T7" s="32" t="inlineStr"/>
@@ -1649,7 +1661,7 @@
       </c>
       <c r="V7" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W7" s="34" t="inlineStr"/>
@@ -1666,7 +1678,7 @@
       <c r="AD7" s="38" t="inlineStr"/>
       <c r="AE7" s="38" t="inlineStr">
         <is>
-          <t>splice sp_canl: node of the wire list (SoT)</t>
+          <t>splice sp_canh: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF7" s="38" t="inlineStr">
@@ -1684,7 +1696,7 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>wc_term3</t>
+          <t>wc_term2</t>
         </is>
       </c>
       <c r="C8" s="39" t="inlineStr">
@@ -1700,20 +1712,20 @@
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>r_term_end</t>
+          <t>r_term_ecu</t>
         </is>
       </c>
       <c r="G8" s="42" t="inlineStr">
         <is>
-          <t>r_term_end</t>
+          <t>r_term_ecu</t>
         </is>
       </c>
       <c r="H8" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="42" t="inlineStr">
         <is>
-          <t>Lambda 120R CAN H</t>
+          <t>ECU 120R CAN L</t>
         </is>
       </c>
       <c r="J8" s="42" t="inlineStr"/>
@@ -1724,34 +1736,34 @@
       </c>
       <c r="L8" s="44" t="inlineStr">
         <is>
-          <t>sp_canh_lam</t>
+          <t>sp_canl</t>
         </is>
       </c>
       <c r="M8" s="45" t="inlineStr">
         <is>
-          <t>splice sp_canh_lam (CAN H join)</t>
+          <t>splice sp_canl (CAN L join)</t>
         </is>
       </c>
       <c r="N8" s="44" t="inlineStr"/>
       <c r="O8" s="45" t="inlineStr">
         <is>
-          <t>Lambda 120R CAN H</t>
+          <t>ECU 120R CAN L</t>
         </is>
       </c>
       <c r="P8" s="45" t="inlineStr"/>
       <c r="Q8" s="46" t="inlineStr">
         <is>
-          <t>ECU-COMMS.C3</t>
+          <t>ECU-COMMS.C4</t>
         </is>
       </c>
       <c r="R8" s="47" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda (ECU-COMMS C3)</t>
+          <t>CAN L to CAN-Lambda (ECU-COMMS C4)</t>
         </is>
       </c>
       <c r="S8" s="48" t="inlineStr">
         <is>
-          <t>sp_canh_lam</t>
+          <t>sp_canl</t>
         </is>
       </c>
       <c r="T8" s="48" t="inlineStr"/>
@@ -1760,7 +1772,7 @@
       </c>
       <c r="V8" s="50" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="W8" s="50" t="inlineStr"/>
@@ -1777,7 +1789,7 @@
       <c r="AD8" s="54" t="inlineStr"/>
       <c r="AE8" s="54" t="inlineStr">
         <is>
-          <t>splice sp_canh_lam: node of the wire list (SoT)</t>
+          <t>splice sp_canl: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF8" s="54" t="inlineStr">
@@ -1795,7 +1807,7 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>wc_term4</t>
+          <t>wc_term3</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -1820,11 +1832,11 @@
         </is>
       </c>
       <c r="H9" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="26" t="inlineStr">
         <is>
-          <t>Lambda 120R CAN L</t>
+          <t>Lambda 120R CAN H</t>
         </is>
       </c>
       <c r="J9" s="26" t="inlineStr"/>
@@ -1835,34 +1847,34 @@
       </c>
       <c r="L9" s="28" t="inlineStr">
         <is>
-          <t>sp_canl_lam</t>
+          <t>sp_canh_lam</t>
         </is>
       </c>
       <c r="M9" s="29" t="inlineStr">
         <is>
-          <t>splice sp_canl_lam (CAN L join)</t>
+          <t>splice sp_canh_lam (CAN H join)</t>
         </is>
       </c>
       <c r="N9" s="28" t="inlineStr"/>
       <c r="O9" s="29" t="inlineStr">
         <is>
-          <t>Lambda 120R CAN L</t>
+          <t>Lambda 120R CAN H</t>
         </is>
       </c>
       <c r="P9" s="29" t="inlineStr"/>
       <c r="Q9" s="30" t="inlineStr">
         <is>
-          <t>ECU-COMMS.C4</t>
+          <t>ECU-COMMS.C3</t>
         </is>
       </c>
       <c r="R9" s="31" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda (ECU-COMMS C4)</t>
+          <t>CAN H to CAN-Lambda (ECU-COMMS C3)</t>
         </is>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
-          <t>sp_canl_lam</t>
+          <t>sp_canh_lam</t>
         </is>
       </c>
       <c r="T9" s="32" t="inlineStr"/>
@@ -1871,7 +1883,7 @@
       </c>
       <c r="V9" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W9" s="34" t="inlineStr"/>
@@ -1888,7 +1900,7 @@
       <c r="AD9" s="38" t="inlineStr"/>
       <c r="AE9" s="38" t="inlineStr">
         <is>
-          <t>splice sp_canl_lam: node of the wire list (SoT)</t>
+          <t>splice sp_canh_lam: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF9" s="38" t="inlineStr">
@@ -1906,7 +1918,7 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>wc_h_csb</t>
+          <t>wc_term4</t>
         </is>
       </c>
       <c r="C10" s="39" t="inlineStr">
@@ -1914,83 +1926,75 @@
           <t>CAN</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
-        <is>
-          <t>CSB3</t>
-        </is>
-      </c>
+      <c r="D10" s="39" t="inlineStr"/>
       <c r="E10" s="40" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>resistor</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>sp_canh</t>
+          <t>r_term_end</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
         <is>
-          <t>splice sp_canh (CAN H join)</t>
-        </is>
-      </c>
-      <c r="H10" s="41" t="inlineStr"/>
+          <t>r_term_end</t>
+        </is>
+      </c>
+      <c r="H10" s="41" t="n">
+        <v>2</v>
+      </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
-          <t>CAN H to CSB3</t>
+          <t>Lambda 120R CAN L</t>
         </is>
       </c>
       <c r="J10" s="42" t="inlineStr"/>
       <c r="K10" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L10" s="44" t="inlineStr">
         <is>
-          <t>csb3io</t>
+          <t>sp_canl_lam</t>
         </is>
       </c>
       <c r="M10" s="45" t="inlineStr">
         <is>
-          <t>CSB3</t>
-        </is>
-      </c>
-      <c r="N10" s="44" t="n">
-        <v>5</v>
-      </c>
+          <t>splice sp_canl_lam (CAN L join)</t>
+        </is>
+      </c>
+      <c r="N10" s="44" t="inlineStr"/>
       <c r="O10" s="45" t="inlineStr">
         <is>
-          <t>CAN H to CSB3</t>
+          <t>Lambda 120R CAN L</t>
         </is>
       </c>
       <c r="P10" s="45" t="inlineStr"/>
       <c r="Q10" s="46" t="inlineStr">
         <is>
-          <t>ECU-COMMS.C3</t>
+          <t>ECU-COMMS.C4</t>
         </is>
       </c>
       <c r="R10" s="47" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda (ECU-COMMS C3)</t>
+          <t>CAN L to CAN-Lambda (ECU-COMMS C4)</t>
         </is>
       </c>
       <c r="S10" s="48" t="inlineStr">
         <is>
-          <t>sp_canh</t>
-        </is>
-      </c>
-      <c r="T10" s="48" t="inlineStr">
-        <is>
-          <t>cab_can_csb</t>
-        </is>
-      </c>
+          <t>sp_canl_lam</t>
+        </is>
+      </c>
+      <c r="T10" s="48" t="inlineStr"/>
       <c r="U10" s="49" t="n">
         <v>20</v>
       </c>
       <c r="V10" s="50" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="W10" s="50" t="inlineStr"/>
@@ -2007,7 +2011,7 @@
       <c r="AD10" s="54" t="inlineStr"/>
       <c r="AE10" s="54" t="inlineStr">
         <is>
-          <t>splice sp_canh: node of the wire list (SoT)</t>
+          <t>splice sp_canl_lam: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF10" s="54" t="inlineStr">
@@ -2015,11 +2019,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG10" s="54" t="inlineStr">
-        <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_h_csb on CAN, ? mm; wc_h_csb_csb on CSB3, 150 mm)</t>
-        </is>
-      </c>
+      <c r="AG10" s="54" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>wc_h_clu</t>
+          <t>wc_h_csb</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -2037,7 +2037,11 @@
           <t>CAN</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr"/>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>CSB3</t>
+        </is>
+      </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
           <t>splice</t>
@@ -2056,33 +2060,31 @@
       <c r="H11" s="25" t="inlineStr"/>
       <c r="I11" s="26" t="inlineStr">
         <is>
-          <t>CAN H to cluster</t>
+          <t>CAN H to CSB3</t>
         </is>
       </c>
       <c r="J11" s="26" t="inlineStr"/>
       <c r="K11" s="27" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L11" s="28" t="inlineStr">
         <is>
-          <t>t_cluster_can</t>
+          <t>csb3io</t>
         </is>
       </c>
       <c r="M11" s="29" t="inlineStr">
         <is>
-          <t>Cluster CAN board CANH + CANL pins (old meter spot)</t>
-        </is>
-      </c>
-      <c r="N11" s="28" t="inlineStr">
-        <is>
-          <t>CANH</t>
-        </is>
+          <t>CSB3</t>
+        </is>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>5</v>
       </c>
       <c r="O11" s="29" t="inlineStr">
         <is>
-          <t>CAN H to cluster</t>
+          <t>CAN H to CSB3</t>
         </is>
       </c>
       <c r="P11" s="29" t="inlineStr"/>
@@ -2103,7 +2105,7 @@
       </c>
       <c r="T11" s="32" t="inlineStr">
         <is>
-          <t>cab_can_clu</t>
+          <t>cab_can_csb</t>
         </is>
       </c>
       <c r="U11" s="33" t="n">
@@ -2128,7 +2130,7 @@
       <c r="AD11" s="38" t="inlineStr"/>
       <c r="AE11" s="38" t="inlineStr">
         <is>
-          <t>splice sp_canh: node of the wire list (SoT); end t_cluster_can: end row of the wire list (SoT)</t>
+          <t>splice sp_canh: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF11" s="38" t="inlineStr">
@@ -2136,7 +2138,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG11" s="38" t="inlineStr"/>
+      <c r="AG11" s="38" t="inlineStr">
+        <is>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_h_csb on CAN, ? mm; wc_h_csb_csb on CSB3, 150 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="39" t="inlineStr">
@@ -2146,7 +2152,7 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t>wc_h_rd</t>
+          <t>wc_h_clu</t>
         </is>
       </c>
       <c r="C12" s="39" t="inlineStr">
@@ -2173,7 +2179,7 @@
       <c r="H12" s="41" t="inlineStr"/>
       <c r="I12" s="42" t="inlineStr">
         <is>
-          <t>CAN H to RealDash Pi</t>
+          <t>CAN H to cluster</t>
         </is>
       </c>
       <c r="J12" s="42" t="inlineStr"/>
@@ -2184,12 +2190,12 @@
       </c>
       <c r="L12" s="44" t="inlineStr">
         <is>
-          <t>t_realdash_can</t>
+          <t>t_cluster_can</t>
         </is>
       </c>
       <c r="M12" s="45" t="inlineStr">
         <is>
-          <t>Pi USB-CAN adapter CANH + CANL pins (center dash)</t>
+          <t>Cluster CAN board CANH + CANL pins (old meter spot)</t>
         </is>
       </c>
       <c r="N12" s="44" t="inlineStr">
@@ -2199,7 +2205,7 @@
       </c>
       <c r="O12" s="45" t="inlineStr">
         <is>
-          <t>CAN H to RealDash Pi</t>
+          <t>CAN H to cluster</t>
         </is>
       </c>
       <c r="P12" s="45" t="inlineStr"/>
@@ -2220,7 +2226,7 @@
       </c>
       <c r="T12" s="48" t="inlineStr">
         <is>
-          <t>cab_can_rd</t>
+          <t>cab_can_clu</t>
         </is>
       </c>
       <c r="U12" s="49" t="n">
@@ -2245,7 +2251,7 @@
       <c r="AD12" s="54" t="inlineStr"/>
       <c r="AE12" s="54" t="inlineStr">
         <is>
-          <t>splice sp_canh: node of the wire list (SoT); end t_realdash_can: end row of the wire list (SoT)</t>
+          <t>splice sp_canh: node of the wire list (SoT); end t_cluster_can: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF12" s="54" t="inlineStr">
@@ -2263,7 +2269,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>wc_h_lam_pin</t>
+          <t>wc_h_rd</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -2279,42 +2285,44 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>sp_canh_lam</t>
+          <t>sp_canh</t>
         </is>
       </c>
       <c r="G13" s="26" t="inlineStr">
         <is>
-          <t>splice sp_canh_lam (CAN H join)</t>
+          <t>splice sp_canh (CAN H join)</t>
         </is>
       </c>
       <c r="H13" s="25" t="inlineStr"/>
       <c r="I13" s="26" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda</t>
+          <t>CAN H to RealDash Pi</t>
         </is>
       </c>
       <c r="J13" s="26" t="inlineStr"/>
       <c r="K13" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>terminal</t>
         </is>
       </c>
       <c r="L13" s="28" t="inlineStr">
         <is>
-          <t>lambda</t>
+          <t>t_realdash_can</t>
         </is>
       </c>
       <c r="M13" s="29" t="inlineStr">
         <is>
-          <t>CAN-LAMBDA</t>
-        </is>
-      </c>
-      <c r="N13" s="28" t="n">
-        <v>4</v>
+          <t>Pi USB-CAN adapter CANH + CANL pins (center dash)</t>
+        </is>
+      </c>
+      <c r="N13" s="28" t="inlineStr">
+        <is>
+          <t>CANH</t>
+        </is>
       </c>
       <c r="O13" s="29" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda</t>
+          <t>CAN H to RealDash Pi</t>
         </is>
       </c>
       <c r="P13" s="29" t="inlineStr"/>
@@ -2330,10 +2338,14 @@
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
-          <t>sp_canh_lam</t>
-        </is>
-      </c>
-      <c r="T13" s="32" t="inlineStr"/>
+          <t>sp_canh</t>
+        </is>
+      </c>
+      <c r="T13" s="32" t="inlineStr">
+        <is>
+          <t>cab_can_rd</t>
+        </is>
+      </c>
       <c r="U13" s="33" t="n">
         <v>20</v>
       </c>
@@ -2356,7 +2368,7 @@
       <c r="AD13" s="38" t="inlineStr"/>
       <c r="AE13" s="38" t="inlineStr">
         <is>
-          <t>splice sp_canh_lam: node of the wire list (SoT)</t>
+          <t>splice sp_canh: node of the wire list (SoT); end t_realdash_can: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF13" s="38" t="inlineStr">
@@ -2374,7 +2386,7 @@
       </c>
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t>wc_l_csb</t>
+          <t>wc_h_lam_pin</t>
         </is>
       </c>
       <c r="C14" s="39" t="inlineStr">
@@ -2382,11 +2394,7 @@
           <t>CAN</t>
         </is>
       </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>CSB3</t>
-        </is>
-      </c>
+      <c r="D14" s="39" t="inlineStr"/>
       <c r="E14" s="40" t="inlineStr">
         <is>
           <t>splice</t>
@@ -2394,18 +2402,18 @@
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>sp_canl</t>
+          <t>sp_canh_lam</t>
         </is>
       </c>
       <c r="G14" s="42" t="inlineStr">
         <is>
-          <t>splice sp_canl (CAN L join)</t>
+          <t>splice sp_canh_lam (CAN H join)</t>
         </is>
       </c>
       <c r="H14" s="41" t="inlineStr"/>
       <c r="I14" s="42" t="inlineStr">
         <is>
-          <t>CAN L to CSB3</t>
+          <t>CAN H to CAN-Lambda</t>
         </is>
       </c>
       <c r="J14" s="42" t="inlineStr"/>
@@ -2416,49 +2424,45 @@
       </c>
       <c r="L14" s="44" t="inlineStr">
         <is>
-          <t>csb3io</t>
+          <t>lambda</t>
         </is>
       </c>
       <c r="M14" s="45" t="inlineStr">
         <is>
-          <t>CSB3</t>
+          <t>CAN-LAMBDA</t>
         </is>
       </c>
       <c r="N14" s="44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O14" s="45" t="inlineStr">
         <is>
-          <t>CAN L to CSB3</t>
+          <t>CAN H to CAN-Lambda</t>
         </is>
       </c>
       <c r="P14" s="45" t="inlineStr"/>
       <c r="Q14" s="46" t="inlineStr">
         <is>
-          <t>ECU-COMMS.C4</t>
+          <t>ECU-COMMS.C3</t>
         </is>
       </c>
       <c r="R14" s="47" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda (ECU-COMMS C4)</t>
+          <t>CAN H to CAN-Lambda (ECU-COMMS C3)</t>
         </is>
       </c>
       <c r="S14" s="48" t="inlineStr">
         <is>
-          <t>sp_canl</t>
-        </is>
-      </c>
-      <c r="T14" s="48" t="inlineStr">
-        <is>
-          <t>cab_can_csb</t>
-        </is>
-      </c>
+          <t>sp_canh_lam</t>
+        </is>
+      </c>
+      <c r="T14" s="48" t="inlineStr"/>
       <c r="U14" s="49" t="n">
         <v>20</v>
       </c>
       <c r="V14" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W14" s="50" t="inlineStr"/>
@@ -2475,7 +2479,7 @@
       <c r="AD14" s="54" t="inlineStr"/>
       <c r="AE14" s="54" t="inlineStr">
         <is>
-          <t>splice sp_canl: node of the wire list (SoT)</t>
+          <t>splice sp_canh_lam: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF14" s="54" t="inlineStr">
@@ -2483,11 +2487,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG14" s="54" t="inlineStr">
-        <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_l_csb on CAN, ? mm; wc_l_csb_csb on CSB3, 150 mm)</t>
-        </is>
-      </c>
+      <c r="AG14" s="54" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>wc_l_clu</t>
+          <t>wc_l_csb</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -2505,7 +2505,11 @@
           <t>CAN</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr"/>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>CSB3</t>
+        </is>
+      </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
           <t>splice</t>
@@ -2524,33 +2528,31 @@
       <c r="H15" s="25" t="inlineStr"/>
       <c r="I15" s="26" t="inlineStr">
         <is>
-          <t>CAN L to cluster</t>
+          <t>CAN L to CSB3</t>
         </is>
       </c>
       <c r="J15" s="26" t="inlineStr"/>
       <c r="K15" s="27" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L15" s="28" t="inlineStr">
         <is>
-          <t>t_cluster_can</t>
+          <t>csb3io</t>
         </is>
       </c>
       <c r="M15" s="29" t="inlineStr">
         <is>
-          <t>Cluster CAN board CANH + CANL pins (old meter spot)</t>
-        </is>
-      </c>
-      <c r="N15" s="28" t="inlineStr">
-        <is>
-          <t>CANL</t>
-        </is>
+          <t>CSB3</t>
+        </is>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>6</v>
       </c>
       <c r="O15" s="29" t="inlineStr">
         <is>
-          <t>CAN L to cluster</t>
+          <t>CAN L to CSB3</t>
         </is>
       </c>
       <c r="P15" s="29" t="inlineStr"/>
@@ -2571,7 +2573,7 @@
       </c>
       <c r="T15" s="32" t="inlineStr">
         <is>
-          <t>cab_can_clu</t>
+          <t>cab_can_csb</t>
         </is>
       </c>
       <c r="U15" s="33" t="n">
@@ -2596,7 +2598,7 @@
       <c r="AD15" s="38" t="inlineStr"/>
       <c r="AE15" s="38" t="inlineStr">
         <is>
-          <t>splice sp_canl: node of the wire list (SoT); end t_cluster_can: end row of the wire list (SoT)</t>
+          <t>splice sp_canl: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF15" s="38" t="inlineStr">
@@ -2604,7 +2606,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG15" s="38" t="inlineStr"/>
+      <c r="AG15" s="38" t="inlineStr">
+        <is>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_l_csb on CAN, ? mm; wc_l_csb_csb on CSB3, 150 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="39" t="inlineStr">
@@ -2614,7 +2620,7 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t>wc_l_rd</t>
+          <t>wc_l_clu</t>
         </is>
       </c>
       <c r="C16" s="39" t="inlineStr">
@@ -2641,7 +2647,7 @@
       <c r="H16" s="41" t="inlineStr"/>
       <c r="I16" s="42" t="inlineStr">
         <is>
-          <t>CAN L to RealDash Pi</t>
+          <t>CAN L to cluster</t>
         </is>
       </c>
       <c r="J16" s="42" t="inlineStr"/>
@@ -2652,12 +2658,12 @@
       </c>
       <c r="L16" s="44" t="inlineStr">
         <is>
-          <t>t_realdash_can</t>
+          <t>t_cluster_can</t>
         </is>
       </c>
       <c r="M16" s="45" t="inlineStr">
         <is>
-          <t>Pi USB-CAN adapter CANH + CANL pins (center dash)</t>
+          <t>Cluster CAN board CANH + CANL pins (old meter spot)</t>
         </is>
       </c>
       <c r="N16" s="44" t="inlineStr">
@@ -2667,7 +2673,7 @@
       </c>
       <c r="O16" s="45" t="inlineStr">
         <is>
-          <t>CAN L to RealDash Pi</t>
+          <t>CAN L to cluster</t>
         </is>
       </c>
       <c r="P16" s="45" t="inlineStr"/>
@@ -2688,7 +2694,7 @@
       </c>
       <c r="T16" s="48" t="inlineStr">
         <is>
-          <t>cab_can_rd</t>
+          <t>cab_can_clu</t>
         </is>
       </c>
       <c r="U16" s="49" t="n">
@@ -2713,7 +2719,7 @@
       <c r="AD16" s="54" t="inlineStr"/>
       <c r="AE16" s="54" t="inlineStr">
         <is>
-          <t>splice sp_canl: node of the wire list (SoT); end t_realdash_can: end row of the wire list (SoT)</t>
+          <t>splice sp_canl: node of the wire list (SoT); end t_cluster_can: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF16" s="54" t="inlineStr">
@@ -2731,7 +2737,7 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>wc_l_lam_pin</t>
+          <t>wc_l_rd</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -2747,42 +2753,44 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>sp_canl_lam</t>
+          <t>sp_canl</t>
         </is>
       </c>
       <c r="G17" s="26" t="inlineStr">
         <is>
-          <t>splice sp_canl_lam (CAN L join)</t>
+          <t>splice sp_canl (CAN L join)</t>
         </is>
       </c>
       <c r="H17" s="25" t="inlineStr"/>
       <c r="I17" s="26" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda</t>
+          <t>CAN L to RealDash Pi</t>
         </is>
       </c>
       <c r="J17" s="26" t="inlineStr"/>
       <c r="K17" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>terminal</t>
         </is>
       </c>
       <c r="L17" s="28" t="inlineStr">
         <is>
-          <t>lambda</t>
+          <t>t_realdash_can</t>
         </is>
       </c>
       <c r="M17" s="29" t="inlineStr">
         <is>
-          <t>CAN-LAMBDA</t>
-        </is>
-      </c>
-      <c r="N17" s="28" t="n">
-        <v>3</v>
+          <t>Pi USB-CAN adapter CANH + CANL pins (center dash)</t>
+        </is>
+      </c>
+      <c r="N17" s="28" t="inlineStr">
+        <is>
+          <t>CANL</t>
+        </is>
       </c>
       <c r="O17" s="29" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda</t>
+          <t>CAN L to RealDash Pi</t>
         </is>
       </c>
       <c r="P17" s="29" t="inlineStr"/>
@@ -2798,10 +2806,14 @@
       </c>
       <c r="S17" s="32" t="inlineStr">
         <is>
-          <t>sp_canl_lam</t>
-        </is>
-      </c>
-      <c r="T17" s="32" t="inlineStr"/>
+          <t>sp_canl</t>
+        </is>
+      </c>
+      <c r="T17" s="32" t="inlineStr">
+        <is>
+          <t>cab_can_rd</t>
+        </is>
+      </c>
       <c r="U17" s="33" t="n">
         <v>20</v>
       </c>
@@ -2824,7 +2836,7 @@
       <c r="AD17" s="38" t="inlineStr"/>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>splice sp_canl_lam: node of the wire list (SoT)</t>
+          <t>splice sp_canl: node of the wire list (SoT); end t_realdash_can: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
@@ -2837,12 +2849,12 @@
     <row r="18">
       <c r="A18" s="39" t="inlineStr">
         <is>
-          <t>DEV</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>w_dev_clu</t>
+          <t>wc_l_lam_pin</t>
         </is>
       </c>
       <c r="C18" s="39" t="inlineStr">
@@ -2858,71 +2870,73 @@
       </c>
       <c r="F18" s="41" t="inlineStr">
         <is>
-          <t>sp_dev</t>
+          <t>sp_canl_lam</t>
         </is>
       </c>
       <c r="G18" s="42" t="inlineStr">
         <is>
-          <t>splice sp_dev (Dash 12 V split)</t>
+          <t>splice sp_canl_lam (CAN L join)</t>
         </is>
       </c>
       <c r="H18" s="41" t="inlineStr"/>
       <c r="I18" s="42" t="inlineStr">
         <is>
-          <t>Cluster +12 V</t>
+          <t>CAN L to CAN-Lambda</t>
         </is>
       </c>
       <c r="J18" s="42" t="inlineStr"/>
       <c r="K18" s="43" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L18" s="44" t="inlineStr">
         <is>
-          <t>t_cluster_pwr</t>
+          <t>lambda</t>
         </is>
       </c>
       <c r="M18" s="45" t="inlineStr">
         <is>
-          <t>Cluster buck converter IN+ pin (old meter spot)</t>
-        </is>
-      </c>
-      <c r="N18" s="44" t="inlineStr"/>
+          <t>CAN-LAMBDA</t>
+        </is>
+      </c>
+      <c r="N18" s="44" t="n">
+        <v>3</v>
+      </c>
       <c r="O18" s="45" t="inlineStr">
         <is>
-          <t>Cluster +12 V</t>
+          <t>CAN L to CAN-Lambda</t>
         </is>
       </c>
       <c r="P18" s="45" t="inlineStr"/>
       <c r="Q18" s="46" t="inlineStr">
         <is>
-          <t>LOGIC.BUS2-6</t>
+          <t>ECU-COMMS.C4</t>
         </is>
       </c>
       <c r="R18" s="47" t="inlineStr">
         <is>
-          <t>+12V Dash devices +12 V (LOGIC BUS2-6)</t>
+          <t>CAN L to CAN-Lambda (ECU-COMMS C4)</t>
         </is>
       </c>
       <c r="S18" s="48" t="inlineStr">
         <is>
-          <t>sp_dev</t>
+          <t>sp_canl_lam</t>
         </is>
       </c>
       <c r="T18" s="48" t="inlineStr"/>
       <c r="U18" s="49" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V18" s="50" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="W18" s="50" t="inlineStr"/>
       <c r="X18" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Yellow</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y18" s="50" t="inlineStr"/>
@@ -2933,7 +2947,7 @@
       <c r="AD18" s="54" t="inlineStr"/>
       <c r="AE18" s="54" t="inlineStr">
         <is>
-          <t>splice sp_dev: node of the wire list (SoT); end t_cluster_pwr: end row of the wire list (SoT)</t>
+          <t>splice sp_canl_lam: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF18" s="54" t="inlineStr">
@@ -2951,7 +2965,7 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>w_dev_rd</t>
+          <t>w_dev_clu</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -2978,7 +2992,7 @@
       <c r="H19" s="25" t="inlineStr"/>
       <c r="I19" s="26" t="inlineStr">
         <is>
-          <t>RealDash Pi +12 V</t>
+          <t>Cluster +12 V</t>
         </is>
       </c>
       <c r="J19" s="26" t="inlineStr"/>
@@ -2989,18 +3003,18 @@
       </c>
       <c r="L19" s="28" t="inlineStr">
         <is>
-          <t>t_realdash_pwr</t>
+          <t>t_cluster_pwr</t>
         </is>
       </c>
       <c r="M19" s="29" t="inlineStr">
         <is>
-          <t>Pi 12-to-5 V supply IN+ pin (center dash)</t>
+          <t>Cluster buck converter IN+ pin (old meter spot)</t>
         </is>
       </c>
       <c r="N19" s="28" t="inlineStr"/>
       <c r="O19" s="29" t="inlineStr">
         <is>
-          <t>RealDash Pi +12 V</t>
+          <t>Cluster +12 V</t>
         </is>
       </c>
       <c r="P19" s="29" t="inlineStr"/>
@@ -3042,7 +3056,7 @@
       <c r="AD19" s="38" t="inlineStr"/>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>splice sp_dev: node of the wire list (SoT); end t_realdash_pwr: end row of the wire list (SoT)</t>
+          <t>splice sp_dev: node of the wire list (SoT); end t_cluster_pwr: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
@@ -3055,12 +3069,12 @@
     <row r="20">
       <c r="A20" s="39" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>DEV</t>
         </is>
       </c>
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>cab_can_clu_sh</t>
+          <t>w_dev_rd</t>
         </is>
       </c>
       <c r="C20" s="39" t="inlineStr">
@@ -3076,73 +3090,71 @@
       </c>
       <c r="F20" s="41" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
+          <t>sp_dev</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
         <is>
-          <t>splice sp_shield_can (CAN screen join)</t>
+          <t>splice sp_dev (Dash 12 V split)</t>
         </is>
       </c>
       <c r="H20" s="41" t="inlineStr"/>
       <c r="I20" s="42" t="inlineStr">
         <is>
-          <t>Cluster CAN shield</t>
+          <t>RealDash Pi +12 V</t>
         </is>
       </c>
       <c r="J20" s="42" t="inlineStr"/>
       <c r="K20" s="43" t="inlineStr">
         <is>
-          <t>cable screen</t>
+          <t>terminal</t>
         </is>
       </c>
       <c r="L20" s="44" t="inlineStr">
         <is>
-          <t>cab_can_clu</t>
+          <t>t_realdash_pwr</t>
         </is>
       </c>
       <c r="M20" s="45" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
+          <t>Pi 12-to-5 V supply IN+ pin (center dash)</t>
         </is>
       </c>
       <c r="N20" s="44" t="inlineStr"/>
       <c r="O20" s="45" t="inlineStr">
         <is>
-          <t>Cluster CAN shield</t>
+          <t>RealDash Pi +12 V</t>
         </is>
       </c>
       <c r="P20" s="45" t="inlineStr"/>
       <c r="Q20" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>LOGIC.BUS2-6</t>
         </is>
       </c>
       <c r="R20" s="47" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
+          <t>+12V Dash devices +12 V (LOGIC BUS2-6)</t>
         </is>
       </c>
       <c r="S20" s="48" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
-        </is>
-      </c>
-      <c r="T20" s="48" t="inlineStr">
-        <is>
-          <t>cab_can_clu</t>
-        </is>
-      </c>
-      <c r="U20" s="49" t="inlineStr"/>
+          <t>sp_dev</t>
+        </is>
+      </c>
+      <c r="T20" s="48" t="inlineStr"/>
+      <c r="U20" s="49" t="n">
+        <v>16</v>
+      </c>
       <c r="V20" s="50" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W20" s="50" t="inlineStr"/>
       <c r="X20" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Yellow-Blue-Yellow</t>
         </is>
       </c>
       <c r="Y20" s="50" t="inlineStr"/>
@@ -3153,7 +3165,7 @@
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_can: node of the wire list (SoT)</t>
+          <t>splice sp_dev: node of the wire list (SoT); end t_realdash_pwr: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
@@ -3161,11 +3173,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG20" s="54" t="inlineStr">
-        <is>
-          <t>screen floats at the far end</t>
-        </is>
-      </c>
+      <c r="AG20" s="54" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
@@ -3175,7 +3183,7 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>cab_can_csb_sh</t>
+          <t>cab_can_clu_sh</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -3183,11 +3191,7 @@
           <t>CAN</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
-        <is>
-          <t>CSB3</t>
-        </is>
-      </c>
+      <c r="D21" s="23" t="inlineStr"/>
       <c r="E21" s="24" t="inlineStr">
         <is>
           <t>splice</t>
@@ -3195,18 +3199,18 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
+          <t>sp_can_sh_clu</t>
         </is>
       </c>
       <c r="G21" s="26" t="inlineStr">
         <is>
-          <t>splice sp_shield_can (CAN screen join)</t>
+          <t>splice sp_can_sh_clu (SP-CAN-SH-CLU)</t>
         </is>
       </c>
       <c r="H21" s="25" t="inlineStr"/>
       <c r="I21" s="26" t="inlineStr">
         <is>
-          <t>CSB3 CAN shield</t>
+          <t>Cluster CAN shield</t>
         </is>
       </c>
       <c r="J21" s="26" t="inlineStr"/>
@@ -3217,7 +3221,7 @@
       </c>
       <c r="L21" s="28" t="inlineStr">
         <is>
-          <t>cab_can_csb_csb</t>
+          <t>cab_can_clu</t>
         </is>
       </c>
       <c r="M21" s="29" t="inlineStr">
@@ -3228,28 +3232,28 @@
       <c r="N21" s="28" t="inlineStr"/>
       <c r="O21" s="29" t="inlineStr">
         <is>
-          <t>CSB3 CAN shield</t>
+          <t>Cluster CAN shield</t>
         </is>
       </c>
       <c r="P21" s="29" t="inlineStr"/>
       <c r="Q21" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="R21" s="31" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
         </is>
       </c>
       <c r="S21" s="32" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
+          <t>sp_can_sh_clu</t>
         </is>
       </c>
       <c r="T21" s="32" t="inlineStr">
         <is>
-          <t>cab_can_csb</t>
+          <t>cab_can_clu</t>
         </is>
       </c>
       <c r="U21" s="33" t="inlineStr"/>
@@ -3272,7 +3276,7 @@
       <c r="AD21" s="38" t="inlineStr"/>
       <c r="AE21" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_can: node of the wire list (SoT)</t>
+          <t>splice sp_can_sh_clu: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF21" s="38" t="inlineStr">
@@ -3282,7 +3286,7 @@
       </c>
       <c r="AG21" s="38" t="inlineStr">
         <is>
-          <t>screen floats at the far end; owner TBD: a half has no length estimate (drawn today as cab_can_csb_sh on CAN, ? mm; cab_can_csb_csb_sh on CSB3, ? mm)</t>
+          <t>screen floats at the far end</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3298,7 @@
       </c>
       <c r="B22" s="39" t="inlineStr">
         <is>
-          <t>cab_can_rd_sh</t>
+          <t>cab_can_csb_sh</t>
         </is>
       </c>
       <c r="C22" s="39" t="inlineStr">
@@ -3302,7 +3306,11 @@
           <t>CAN</t>
         </is>
       </c>
-      <c r="D22" s="39" t="inlineStr"/>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>CSB3</t>
+        </is>
+      </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
           <t>splice</t>
@@ -3310,18 +3318,18 @@
       </c>
       <c r="F22" s="41" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
+          <t>sp_can_sh_csb</t>
         </is>
       </c>
       <c r="G22" s="42" t="inlineStr">
         <is>
-          <t>splice sp_shield_can (CAN screen join)</t>
+          <t>splice sp_can_sh_csb (SP-CAN-SH-CSB)</t>
         </is>
       </c>
       <c r="H22" s="41" t="inlineStr"/>
       <c r="I22" s="42" t="inlineStr">
         <is>
-          <t>Pi CAN shield</t>
+          <t>CSB3 CAN shield</t>
         </is>
       </c>
       <c r="J22" s="42" t="inlineStr"/>
@@ -3332,7 +3340,7 @@
       </c>
       <c r="L22" s="44" t="inlineStr">
         <is>
-          <t>cab_can_rd</t>
+          <t>cab_can_csb_csb</t>
         </is>
       </c>
       <c r="M22" s="45" t="inlineStr">
@@ -3343,28 +3351,28 @@
       <c r="N22" s="44" t="inlineStr"/>
       <c r="O22" s="45" t="inlineStr">
         <is>
-          <t>Pi CAN shield</t>
+          <t>CSB3 CAN shield</t>
         </is>
       </c>
       <c r="P22" s="45" t="inlineStr"/>
       <c r="Q22" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="R22" s="47" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
         </is>
       </c>
       <c r="S22" s="48" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
+          <t>sp_can_sh_csb</t>
         </is>
       </c>
       <c r="T22" s="48" t="inlineStr">
         <is>
-          <t>cab_can_rd</t>
+          <t>cab_can_csb</t>
         </is>
       </c>
       <c r="U22" s="49" t="inlineStr"/>
@@ -3387,7 +3395,7 @@
       <c r="AD22" s="54" t="inlineStr"/>
       <c r="AE22" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_can: node of the wire list (SoT)</t>
+          <t>splice sp_can_sh_csb: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF22" s="54" t="inlineStr">
@@ -3397,19 +3405,19 @@
       </c>
       <c r="AG22" s="54" t="inlineStr">
         <is>
-          <t>screen floats at the far end</t>
+          <t>screen floats at the far end; owner TBD: a half has no length estimate (drawn today as cab_can_csb_sh on CAN, ? mm; cab_can_csb_csb_sh on CSB3, ? mm)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>DEV</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>w_gnd_clu</t>
+          <t>cab_can_rd_sh</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -3420,77 +3428,81 @@
       <c r="D23" s="23" t="inlineStr"/>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>t_cluster_gnd_lead</t>
+          <t>sp_can_sh_rd</t>
         </is>
       </c>
       <c r="G23" s="26" t="inlineStr">
         <is>
-          <t>Cluster buck converter IN- pin (old meter spot)</t>
+          <t>splice sp_can_sh_rd (SP-CAN-SH-RD)</t>
         </is>
       </c>
       <c r="H23" s="25" t="inlineStr"/>
       <c r="I23" s="26" t="inlineStr">
         <is>
-          <t>Cluster ground</t>
+          <t>Pi CAN shield</t>
         </is>
       </c>
       <c r="J23" s="26" t="inlineStr"/>
       <c r="K23" s="27" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="L23" s="28" t="inlineStr">
         <is>
-          <t>t_cluster_gnd</t>
+          <t>cab_can_rd</t>
         </is>
       </c>
       <c r="M23" s="29" t="inlineStr">
         <is>
-          <t>Ground point IF, I/P brace RH (EWD ground point IF, p.42)</t>
+          <t>cable screen (one end only)</t>
         </is>
       </c>
       <c r="N23" s="28" t="inlineStr"/>
       <c r="O23" s="29" t="inlineStr">
         <is>
-          <t>Cluster ground</t>
+          <t>Pi CAN shield</t>
         </is>
       </c>
       <c r="P23" s="29" t="inlineStr"/>
       <c r="Q23" s="30" t="inlineStr">
         <is>
-          <t>GND.t_cluster_gnd</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="R23" s="31" t="inlineStr">
         <is>
-          <t>Chassis GND (Ground point IF, I/P brace RH (EWD ground point IF, p.42))</t>
-        </is>
-      </c>
-      <c r="S23" s="32" t="inlineStr"/>
-      <c r="T23" s="32" t="inlineStr"/>
-      <c r="U23" s="33" t="n">
-        <v>16</v>
-      </c>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
+        </is>
+      </c>
+      <c r="S23" s="32" t="inlineStr">
+        <is>
+          <t>sp_can_sh_rd</t>
+        </is>
+      </c>
+      <c r="T23" s="32" t="inlineStr">
+        <is>
+          <t>cab_can_rd</t>
+        </is>
+      </c>
+      <c r="U23" s="33" t="inlineStr"/>
       <c r="V23" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="W23" s="34" t="inlineStr"/>
       <c r="X23" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Yellow</t>
-        </is>
-      </c>
-      <c r="Y23" s="34" t="n">
-        <v>1320</v>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="Y23" s="34" t="inlineStr"/>
       <c r="Z23" s="35" t="inlineStr"/>
       <c r="AA23" s="36" t="inlineStr"/>
       <c r="AB23" s="37" t="inlineStr"/>
@@ -3498,7 +3510,7 @@
       <c r="AD23" s="38" t="inlineStr"/>
       <c r="AE23" s="38" t="inlineStr">
         <is>
-          <t>end t_cluster_gnd_lead: end row of the wire list (SoT); end t_cluster_gnd: end row of the wire list (SoT)</t>
+          <t>splice sp_can_sh_rd: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF23" s="38" t="inlineStr">
@@ -3506,17 +3518,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG23" s="38" t="inlineStr"/>
+      <c r="AG23" s="38" t="inlineStr">
+        <is>
+          <t>screen floats at the far end</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="39" t="inlineStr">
         <is>
-          <t>DEV</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B24" s="39" t="inlineStr">
         <is>
-          <t>w_gnd_rd</t>
+          <t>w_shd_can_csb</t>
         </is>
       </c>
       <c r="C24" s="39" t="inlineStr">
@@ -3527,76 +3543,84 @@
       <c r="D24" s="39" t="inlineStr"/>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F24" s="41" t="inlineStr">
         <is>
-          <t>t_realdash_gnd_lead</t>
+          <t>sp_can_sh_clu</t>
         </is>
       </c>
       <c r="G24" s="42" t="inlineStr">
         <is>
-          <t>Pi 12-to-5 V supply IN- pin (center dash)</t>
+          <t>splice sp_can_sh_clu (SP-CAN-SH-CLU)</t>
         </is>
       </c>
       <c r="H24" s="41" t="inlineStr"/>
       <c r="I24" s="42" t="inlineStr">
         <is>
-          <t>RealDash Pi ground</t>
+          <t>CAN screen trunk</t>
         </is>
       </c>
       <c r="J24" s="42" t="inlineStr"/>
       <c r="K24" s="43" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L24" s="44" t="inlineStr">
         <is>
-          <t>t_realdash_gnd</t>
+          <t>sp_can_sh_csb</t>
         </is>
       </c>
       <c r="M24" s="45" t="inlineStr">
         <is>
-          <t>Ground point IF, I/P brace RH (EWD ground point IF, p.42)</t>
+          <t>splice sp_can_sh_csb (SP-CAN-SH-CSB)</t>
         </is>
       </c>
       <c r="N24" s="44" t="inlineStr"/>
       <c r="O24" s="45" t="inlineStr">
         <is>
-          <t>RealDash Pi ground</t>
+          <t>CAN screen trunk</t>
         </is>
       </c>
       <c r="P24" s="45" t="inlineStr"/>
       <c r="Q24" s="46" t="inlineStr">
         <is>
-          <t>GND.t_cluster_gnd</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="R24" s="47" t="inlineStr">
         <is>
-          <t>Chassis GND (Ground point IF, I/P brace RH (EWD ground point IF, p.42))</t>
-        </is>
-      </c>
-      <c r="S24" s="48" t="inlineStr"/>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
+        </is>
+      </c>
+      <c r="S24" s="48" t="inlineStr">
+        <is>
+          <t>sp_can_sh_csb</t>
+        </is>
+      </c>
       <c r="T24" s="48" t="inlineStr"/>
       <c r="U24" s="49" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V24" s="50" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="W24" s="50" t="inlineStr"/>
+      <c r="W24" s="50" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
       <c r="X24" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Yellow</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y24" s="50" t="n">
-        <v>600</v>
+        <v>190</v>
       </c>
       <c r="Z24" s="51" t="inlineStr"/>
       <c r="AA24" s="52" t="inlineStr"/>
@@ -3605,7 +3629,7 @@
       <c r="AD24" s="54" t="inlineStr"/>
       <c r="AE24" s="54" t="inlineStr">
         <is>
-          <t>end t_realdash_gnd_lead: end row of the wire list (SoT); end t_realdash_gnd: end row of the wire list (SoT)</t>
+          <t>splice sp_can_sh_clu: node of the wire list (SoT); splice sp_can_sh_csb: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF24" s="54" t="inlineStr">
@@ -3613,11 +3637,23 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG24" s="54" t="inlineStr"/>
+      <c r="AG24" s="54" t="inlineStr">
+        <is>
+          <t>trunk drain segment; one drain wire in the build, the node drains are soldered on (R30)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr"/>
-      <c r="B25" s="23" t="inlineStr"/>
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>w_shd_can_rd</t>
+        </is>
+      </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
           <t>CAN</t>
@@ -3626,35 +3662,47 @@
       <c r="D25" s="23" t="inlineStr"/>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>ecu_com</t>
+          <t>sp_can_sh_csb</t>
         </is>
       </c>
       <c r="G25" s="26" t="inlineStr">
         <is>
-          <t>ECU COMMS</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
+          <t>splice sp_can_sh_csb (SP-CAN-SH-CSB)</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="inlineStr"/>
       <c r="I25" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>CAN screen trunk</t>
         </is>
       </c>
       <c r="J25" s="26" t="inlineStr"/>
-      <c r="K25" s="27" t="inlineStr"/>
-      <c r="L25" s="28" t="inlineStr"/>
-      <c r="M25" s="29" t="inlineStr"/>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t>splice</t>
+        </is>
+      </c>
+      <c r="L25" s="28" t="inlineStr">
+        <is>
+          <t>sp_can_sh_rd</t>
+        </is>
+      </c>
+      <c r="M25" s="29" t="inlineStr">
+        <is>
+          <t>splice sp_can_sh_rd (SP-CAN-SH-RD)</t>
+        </is>
+      </c>
       <c r="N25" s="28" t="inlineStr"/>
-      <c r="O25" s="29" t="inlineStr"/>
+      <c r="O25" s="29" t="inlineStr">
+        <is>
+          <t>CAN screen trunk</t>
+        </is>
+      </c>
       <c r="P25" s="29" t="inlineStr"/>
       <c r="Q25" s="30" t="inlineStr">
         <is>
@@ -3663,32 +3711,68 @@
       </c>
       <c r="R25" s="31" t="inlineStr">
         <is>
-          <t>spare (ECU-COMMS C1)</t>
-        </is>
-      </c>
-      <c r="S25" s="32" t="inlineStr"/>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
+        </is>
+      </c>
+      <c r="S25" s="32" t="inlineStr">
+        <is>
+          <t>sp_can_sh_rd</t>
+        </is>
+      </c>
       <c r="T25" s="32" t="inlineStr"/>
-      <c r="U25" s="33" t="inlineStr"/>
-      <c r="V25" s="34" t="inlineStr"/>
-      <c r="W25" s="34" t="inlineStr"/>
-      <c r="X25" s="34" t="inlineStr"/>
-      <c r="Y25" s="34" t="inlineStr"/>
+      <c r="U25" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="V25" s="34" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W25" s="34" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="X25" s="34" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="Y25" s="34" t="n">
+        <v>30</v>
+      </c>
       <c r="Z25" s="35" t="inlineStr"/>
       <c r="AA25" s="36" t="inlineStr"/>
       <c r="AB25" s="37" t="inlineStr"/>
       <c r="AC25" s="38" t="inlineStr"/>
       <c r="AD25" s="38" t="inlineStr"/>
-      <c r="AE25" s="38" t="inlineStr"/>
+      <c r="AE25" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_can_sh_csb: node of the wire list (SoT); splice sp_can_sh_rd: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF25" s="38" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AG25" s="38" t="inlineStr"/>
+      <c r="AG25" s="38" t="inlineStr">
+        <is>
+          <t>trunk drain segment; one drain wire in the build, the node drains are soldered on (R30)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr"/>
-      <c r="B26" s="39" t="inlineStr"/>
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>w_shd_can_bh</t>
+        </is>
+      </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
           <t>CAN</t>
@@ -3697,69 +3781,117 @@
       <c r="D26" s="39" t="inlineStr"/>
       <c r="E26" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F26" s="41" t="inlineStr">
         <is>
-          <t>ecu_com</t>
+          <t>sp_can_sh_clu</t>
         </is>
       </c>
       <c r="G26" s="42" t="inlineStr">
         <is>
-          <t>ECU COMMS</t>
-        </is>
-      </c>
-      <c r="H26" s="41" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
+          <t>splice sp_can_sh_clu (SP-CAN-SH-CLU)</t>
+        </is>
+      </c>
+      <c r="H26" s="41" t="inlineStr"/>
       <c r="I26" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>CAN screen trunk</t>
         </is>
       </c>
       <c r="J26" s="42" t="inlineStr"/>
-      <c r="K26" s="43" t="inlineStr"/>
-      <c r="L26" s="44" t="inlineStr"/>
-      <c r="M26" s="45" t="inlineStr"/>
+      <c r="K26" s="43" t="inlineStr">
+        <is>
+          <t>splice</t>
+        </is>
+      </c>
+      <c r="L26" s="44" t="inlineStr">
+        <is>
+          <t>sp_can_sh_bh</t>
+        </is>
+      </c>
+      <c r="M26" s="45" t="inlineStr">
+        <is>
+          <t>splice sp_can_sh_bh (SP-CAN-SH-BH)</t>
+        </is>
+      </c>
       <c r="N26" s="44" t="inlineStr"/>
-      <c r="O26" s="45" t="inlineStr"/>
+      <c r="O26" s="45" t="inlineStr">
+        <is>
+          <t>CAN screen trunk</t>
+        </is>
+      </c>
       <c r="P26" s="45" t="inlineStr"/>
       <c r="Q26" s="46" t="inlineStr">
         <is>
-          <t>ECU-COMMS.C2</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="R26" s="47" t="inlineStr">
         <is>
-          <t>spare (ECU-COMMS C2)</t>
-        </is>
-      </c>
-      <c r="S26" s="48" t="inlineStr"/>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
+        </is>
+      </c>
+      <c r="S26" s="48" t="inlineStr">
+        <is>
+          <t>sp_can_sh_bh</t>
+        </is>
+      </c>
       <c r="T26" s="48" t="inlineStr"/>
-      <c r="U26" s="49" t="inlineStr"/>
-      <c r="V26" s="50" t="inlineStr"/>
-      <c r="W26" s="50" t="inlineStr"/>
-      <c r="X26" s="50" t="inlineStr"/>
-      <c r="Y26" s="50" t="inlineStr"/>
+      <c r="U26" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="V26" s="50" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W26" s="50" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="X26" s="50" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="Y26" s="50" t="n">
+        <v>160</v>
+      </c>
       <c r="Z26" s="51" t="inlineStr"/>
       <c r="AA26" s="52" t="inlineStr"/>
       <c r="AB26" s="53" t="inlineStr"/>
       <c r="AC26" s="54" t="inlineStr"/>
       <c r="AD26" s="54" t="inlineStr"/>
-      <c r="AE26" s="54" t="inlineStr"/>
+      <c r="AE26" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_can_sh_clu: node of the wire list (SoT); splice sp_can_sh_bh: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF26" s="54" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AG26" s="54" t="inlineStr"/>
+      <c r="AG26" s="54" t="inlineStr">
+        <is>
+          <t>trunk drain segment; one drain wire in the build, the node drains are soldered on (R30)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr"/>
-      <c r="B27" s="23" t="inlineStr"/>
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>w_gnd_clu</t>
+        </is>
+      </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
           <t>CAN</t>
@@ -3768,59 +3900,87 @@
       <c r="D27" s="23" t="inlineStr"/>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>terminal</t>
         </is>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>ecu_com</t>
+          <t>t_cluster_gnd_lead</t>
         </is>
       </c>
       <c r="G27" s="26" t="inlineStr">
         <is>
-          <t>ECU COMMS</t>
-        </is>
-      </c>
-      <c r="H27" s="25" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
+          <t>Cluster buck converter IN- pin (old meter spot)</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="inlineStr"/>
       <c r="I27" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>Cluster ground</t>
         </is>
       </c>
       <c r="J27" s="26" t="inlineStr"/>
-      <c r="K27" s="27" t="inlineStr"/>
-      <c r="L27" s="28" t="inlineStr"/>
-      <c r="M27" s="29" t="inlineStr"/>
+      <c r="K27" s="27" t="inlineStr">
+        <is>
+          <t>terminal</t>
+        </is>
+      </c>
+      <c r="L27" s="28" t="inlineStr">
+        <is>
+          <t>t_cluster_gnd</t>
+        </is>
+      </c>
+      <c r="M27" s="29" t="inlineStr">
+        <is>
+          <t>Ground point IF, I/P brace RH (EWD ground point IF, p.42)</t>
+        </is>
+      </c>
       <c r="N27" s="28" t="inlineStr"/>
-      <c r="O27" s="29" t="inlineStr"/>
+      <c r="O27" s="29" t="inlineStr">
+        <is>
+          <t>Cluster ground</t>
+        </is>
+      </c>
       <c r="P27" s="29" t="inlineStr"/>
       <c r="Q27" s="30" t="inlineStr">
         <is>
-          <t>ECU-COMMS.C5</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R27" s="31" t="inlineStr">
         <is>
-          <t>spare (ECU-COMMS C5)</t>
+          <t>Chassis GND (Ground point IF, I/P brace RH (EWD ground point IF, p.42))</t>
         </is>
       </c>
       <c r="S27" s="32" t="inlineStr"/>
       <c r="T27" s="32" t="inlineStr"/>
-      <c r="U27" s="33" t="inlineStr"/>
-      <c r="V27" s="34" t="inlineStr"/>
+      <c r="U27" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="V27" s="34" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
       <c r="W27" s="34" t="inlineStr"/>
-      <c r="X27" s="34" t="inlineStr"/>
-      <c r="Y27" s="34" t="inlineStr"/>
+      <c r="X27" s="34" t="inlineStr">
+        <is>
+          <t>Yellow-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="Y27" s="34" t="n">
+        <v>1320</v>
+      </c>
       <c r="Z27" s="35" t="inlineStr"/>
       <c r="AA27" s="36" t="inlineStr"/>
       <c r="AB27" s="37" t="inlineStr"/>
       <c r="AC27" s="38" t="inlineStr"/>
       <c r="AD27" s="38" t="inlineStr"/>
-      <c r="AE27" s="38" t="inlineStr"/>
+      <c r="AE27" s="38" t="inlineStr">
+        <is>
+          <t>end t_cluster_gnd_lead: end row of the wire list (SoT); end t_cluster_gnd: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF27" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3829,8 +3989,16 @@
       <c r="AG27" s="38" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr"/>
-      <c r="B28" s="39" t="inlineStr"/>
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>w_gnd_rd</t>
+        </is>
+      </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>CAN</t>
@@ -3839,59 +4007,87 @@
       <c r="D28" s="39" t="inlineStr"/>
       <c r="E28" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>terminal</t>
         </is>
       </c>
       <c r="F28" s="41" t="inlineStr">
         <is>
-          <t>ecu_com</t>
+          <t>t_realdash_gnd_lead</t>
         </is>
       </c>
       <c r="G28" s="42" t="inlineStr">
         <is>
-          <t>ECU COMMS</t>
-        </is>
-      </c>
-      <c r="H28" s="41" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
+          <t>Pi 12-to-5 V supply IN- pin (center dash)</t>
+        </is>
+      </c>
+      <c r="H28" s="41" t="inlineStr"/>
       <c r="I28" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>RealDash Pi ground</t>
         </is>
       </c>
       <c r="J28" s="42" t="inlineStr"/>
-      <c r="K28" s="43" t="inlineStr"/>
-      <c r="L28" s="44" t="inlineStr"/>
-      <c r="M28" s="45" t="inlineStr"/>
+      <c r="K28" s="43" t="inlineStr">
+        <is>
+          <t>terminal</t>
+        </is>
+      </c>
+      <c r="L28" s="44" t="inlineStr">
+        <is>
+          <t>t_realdash_gnd</t>
+        </is>
+      </c>
+      <c r="M28" s="45" t="inlineStr">
+        <is>
+          <t>Ground point IF, I/P brace RH (EWD ground point IF, p.42)</t>
+        </is>
+      </c>
       <c r="N28" s="44" t="inlineStr"/>
-      <c r="O28" s="45" t="inlineStr"/>
+      <c r="O28" s="45" t="inlineStr">
+        <is>
+          <t>RealDash Pi ground</t>
+        </is>
+      </c>
       <c r="P28" s="45" t="inlineStr"/>
       <c r="Q28" s="46" t="inlineStr">
         <is>
-          <t>ECU-COMMS.C6</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R28" s="47" t="inlineStr">
         <is>
-          <t>spare (ECU-COMMS C6)</t>
+          <t>Chassis GND (Ground point IF, I/P brace RH (EWD ground point IF, p.42))</t>
         </is>
       </c>
       <c r="S28" s="48" t="inlineStr"/>
       <c r="T28" s="48" t="inlineStr"/>
-      <c r="U28" s="49" t="inlineStr"/>
-      <c r="V28" s="50" t="inlineStr"/>
+      <c r="U28" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="V28" s="50" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
       <c r="W28" s="50" t="inlineStr"/>
-      <c r="X28" s="50" t="inlineStr"/>
-      <c r="Y28" s="50" t="inlineStr"/>
+      <c r="X28" s="50" t="inlineStr">
+        <is>
+          <t>Yellow-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="Y28" s="50" t="n">
+        <v>600</v>
+      </c>
       <c r="Z28" s="51" t="inlineStr"/>
       <c r="AA28" s="52" t="inlineStr"/>
       <c r="AB28" s="53" t="inlineStr"/>
       <c r="AC28" s="54" t="inlineStr"/>
       <c r="AD28" s="54" t="inlineStr"/>
-      <c r="AE28" s="54" t="inlineStr"/>
+      <c r="AE28" s="54" t="inlineStr">
+        <is>
+          <t>end t_realdash_gnd_lead: end row of the wire list (SoT); end t_realdash_gnd: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF28" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3899,8 +4095,221 @@
       </c>
       <c r="AG28" s="54" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr"/>
+      <c r="B29" s="23" t="inlineStr"/>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr"/>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>ecu_com</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>ECU COMMS</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J29" s="26" t="inlineStr"/>
+      <c r="K29" s="27" t="inlineStr"/>
+      <c r="L29" s="28" t="inlineStr"/>
+      <c r="M29" s="29" t="inlineStr"/>
+      <c r="N29" s="28" t="inlineStr"/>
+      <c r="O29" s="29" t="inlineStr"/>
+      <c r="P29" s="29" t="inlineStr"/>
+      <c r="Q29" s="30" t="inlineStr">
+        <is>
+          <t>ECU-COMMS.C2</t>
+        </is>
+      </c>
+      <c r="R29" s="31" t="inlineStr">
+        <is>
+          <t>spare (ECU-COMMS C2)</t>
+        </is>
+      </c>
+      <c r="S29" s="32" t="inlineStr"/>
+      <c r="T29" s="32" t="inlineStr"/>
+      <c r="U29" s="33" t="inlineStr"/>
+      <c r="V29" s="34" t="inlineStr"/>
+      <c r="W29" s="34" t="inlineStr"/>
+      <c r="X29" s="34" t="inlineStr"/>
+      <c r="Y29" s="34" t="inlineStr"/>
+      <c r="Z29" s="35" t="inlineStr"/>
+      <c r="AA29" s="36" t="inlineStr"/>
+      <c r="AB29" s="37" t="inlineStr"/>
+      <c r="AC29" s="38" t="inlineStr"/>
+      <c r="AD29" s="38" t="inlineStr"/>
+      <c r="AE29" s="38" t="inlineStr"/>
+      <c r="AF29" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG29" s="38" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="inlineStr"/>
+      <c r="B30" s="39" t="inlineStr"/>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr"/>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F30" s="41" t="inlineStr">
+        <is>
+          <t>ecu_com</t>
+        </is>
+      </c>
+      <c r="G30" s="42" t="inlineStr">
+        <is>
+          <t>ECU COMMS</t>
+        </is>
+      </c>
+      <c r="H30" s="41" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="I30" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J30" s="42" t="inlineStr"/>
+      <c r="K30" s="43" t="inlineStr"/>
+      <c r="L30" s="44" t="inlineStr"/>
+      <c r="M30" s="45" t="inlineStr"/>
+      <c r="N30" s="44" t="inlineStr"/>
+      <c r="O30" s="45" t="inlineStr"/>
+      <c r="P30" s="45" t="inlineStr"/>
+      <c r="Q30" s="46" t="inlineStr">
+        <is>
+          <t>ECU-COMMS.C5</t>
+        </is>
+      </c>
+      <c r="R30" s="47" t="inlineStr">
+        <is>
+          <t>spare (ECU-COMMS C5)</t>
+        </is>
+      </c>
+      <c r="S30" s="48" t="inlineStr"/>
+      <c r="T30" s="48" t="inlineStr"/>
+      <c r="U30" s="49" t="inlineStr"/>
+      <c r="V30" s="50" t="inlineStr"/>
+      <c r="W30" s="50" t="inlineStr"/>
+      <c r="X30" s="50" t="inlineStr"/>
+      <c r="Y30" s="50" t="inlineStr"/>
+      <c r="Z30" s="51" t="inlineStr"/>
+      <c r="AA30" s="52" t="inlineStr"/>
+      <c r="AB30" s="53" t="inlineStr"/>
+      <c r="AC30" s="54" t="inlineStr"/>
+      <c r="AD30" s="54" t="inlineStr"/>
+      <c r="AE30" s="54" t="inlineStr"/>
+      <c r="AF30" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG30" s="54" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr"/>
+      <c r="B31" s="23" t="inlineStr"/>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr"/>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>ecu_com</t>
+        </is>
+      </c>
+      <c r="G31" s="26" t="inlineStr">
+        <is>
+          <t>ECU COMMS</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="I31" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J31" s="26" t="inlineStr"/>
+      <c r="K31" s="27" t="inlineStr"/>
+      <c r="L31" s="28" t="inlineStr"/>
+      <c r="M31" s="29" t="inlineStr"/>
+      <c r="N31" s="28" t="inlineStr"/>
+      <c r="O31" s="29" t="inlineStr"/>
+      <c r="P31" s="29" t="inlineStr"/>
+      <c r="Q31" s="30" t="inlineStr">
+        <is>
+          <t>ECU-COMMS.C6</t>
+        </is>
+      </c>
+      <c r="R31" s="31" t="inlineStr">
+        <is>
+          <t>spare (ECU-COMMS C6)</t>
+        </is>
+      </c>
+      <c r="S31" s="32" t="inlineStr"/>
+      <c r="T31" s="32" t="inlineStr"/>
+      <c r="U31" s="33" t="inlineStr"/>
+      <c r="V31" s="34" t="inlineStr"/>
+      <c r="W31" s="34" t="inlineStr"/>
+      <c r="X31" s="34" t="inlineStr"/>
+      <c r="Y31" s="34" t="inlineStr"/>
+      <c r="Z31" s="35" t="inlineStr"/>
+      <c r="AA31" s="36" t="inlineStr"/>
+      <c r="AB31" s="37" t="inlineStr"/>
+      <c r="AC31" s="38" t="inlineStr"/>
+      <c r="AD31" s="38" t="inlineStr"/>
+      <c r="AE31" s="38" t="inlineStr"/>
+      <c r="AF31" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG31" s="38" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AG28"/>
+  <autoFilter ref="A2:AG31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3912,7 +4321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4280,12 +4689,12 @@
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
+          <t>sp_dev</t>
         </is>
       </c>
       <c r="B7" s="55" t="inlineStr">
         <is>
-          <t>CAN screen join - all CAN pair screens to the drain</t>
+          <t>Dash 12 V split - cluster + RealDash Pi, center dash</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -4295,27 +4704,27 @@
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>LOGIC.BUS2-6</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
+          <t>+12V Dash devices +12 V (LOGIC BUS2-6)</t>
         </is>
       </c>
       <c r="F7" s="32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G7" s="32" t="inlineStr">
         <is>
-          <t>20 + shield</t>
+          <t>16+16+16</t>
         </is>
       </c>
       <c r="H7" s="32" t="n">
-        <v>1022</v>
+        <v>7749</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J7" s="56" t="inlineStr">
         <is>
@@ -4324,7 +4733,7 @@
       </c>
       <c r="K7" s="36" t="inlineStr">
         <is>
-          <t>CAN screen join (layout node bp_930)</t>
+          <t>Dash 12 V split (layout node bp_930)</t>
         </is>
       </c>
       <c r="L7" s="38" t="inlineStr">
@@ -4336,12 +4745,12 @@
     <row r="8">
       <c r="A8" s="39" t="inlineStr">
         <is>
-          <t>sp_dev</t>
+          <t>sp_can_sh_clu</t>
         </is>
       </c>
       <c r="B8" s="57" t="inlineStr">
         <is>
-          <t>Dash 12 V split - cluster + RealDash Pi, center dash</t>
+          <t>CAN trunk, cluster branch - SP-CAN-SH-CLU: CAN screen</t>
         </is>
       </c>
       <c r="C8" s="39" t="inlineStr">
@@ -4351,46 +4760,214 @@
       </c>
       <c r="D8" s="46" t="inlineStr">
         <is>
-          <t>LOGIC.BUS2-6</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="E8" s="47" t="inlineStr">
         <is>
-          <t>+12V Dash devices +12 V (LOGIC BUS2-6)</t>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
         </is>
       </c>
       <c r="F8" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="48" t="inlineStr">
+        <is>
+          <t>20+20+20 + shield</t>
+        </is>
+      </c>
+      <c r="H8" s="48" t="n">
+        <v>3066</v>
+      </c>
+      <c r="I8" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" s="58" t="inlineStr">
+        <is>
+          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
+        </is>
+      </c>
+      <c r="K8" s="52" t="inlineStr">
+        <is>
+          <t>CAN trunk, cluster branch (layout node bp_930)</t>
+        </is>
+      </c>
+      <c r="L8" s="54" t="inlineStr">
+        <is>
+          <t>node of the wire list (SoT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>sp_can_sh_csb</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>CAN trunk, CSB3 branch - SP-CAN-SH-CSB: CAN screen</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>ECU-COMMS.C1</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="48" t="inlineStr">
-        <is>
-          <t>16+16+16</t>
-        </is>
-      </c>
-      <c r="H8" s="48" t="n">
-        <v>7749</v>
-      </c>
-      <c r="I8" s="48" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="58" t="inlineStr">
+      <c r="G9" s="32" t="inlineStr">
+        <is>
+          <t>20+20 + shield</t>
+        </is>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>2044</v>
+      </c>
+      <c r="I9" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" s="56" t="inlineStr">
         <is>
           <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
         </is>
       </c>
-      <c r="K8" s="52" t="inlineStr">
-        <is>
-          <t>Dash 12 V split (layout node bp_930)</t>
-        </is>
-      </c>
-      <c r="L8" s="54" t="inlineStr">
+      <c r="K9" s="36" t="inlineStr">
+        <is>
+          <t>CAN trunk, CSB3 branch (layout node bp_1050)</t>
+        </is>
+      </c>
+      <c r="L9" s="38" t="inlineStr">
+        <is>
+          <t>node of the wire list (SoT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>sp_can_sh_rd</t>
+        </is>
+      </c>
+      <c r="B10" s="57" t="inlineStr">
+        <is>
+          <t>CAN trunk, RealDash Pi branch - SP-CAN-SH-RD: CAN screen</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>ECU-COMMS.C1</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="inlineStr">
+        <is>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
+        </is>
+      </c>
+      <c r="F10" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="48" t="inlineStr">
+        <is>
+          <t>20 + shield</t>
+        </is>
+      </c>
+      <c r="H10" s="48" t="n">
+        <v>1022</v>
+      </c>
+      <c r="I10" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="J10" s="58" t="inlineStr">
+        <is>
+          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
+        </is>
+      </c>
+      <c r="K10" s="52" t="inlineStr">
+        <is>
+          <t>CAN trunk, RealDash Pi branch (layout node bp_1050)</t>
+        </is>
+      </c>
+      <c r="L10" s="54" t="inlineStr">
+        <is>
+          <t>node of the wire list (SoT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>sp_can_sh_bh</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>CAN trunk, bulkhead B branch - SP-CAN-SH-BH: CAN screen to CAN-Lambda</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>ECU-COMMS.C1</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>20 + shield</t>
+        </is>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>1022</v>
+      </c>
+      <c r="I11" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" s="56" t="inlineStr">
+        <is>
+          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
+        </is>
+      </c>
+      <c r="K11" s="36" t="inlineStr">
+        <is>
+          <t>CAN trunk, bulkhead B branch (layout node bp_840)</t>
+        </is>
+      </c>
+      <c r="L11" s="38" t="inlineStr">
         <is>
           <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L8"/>
+  <autoFilter ref="A2:L11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/harness/wirelist/CAN-wirelist.xlsx
+++ b/docs/harness/wirelist/CAN-wirelist.xlsx
@@ -1428,11 +1428,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W5" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W5" s="34" t="inlineStr"/>
       <c r="X5" s="34" t="inlineStr">
         <is>
           <t>Yellow</t>
@@ -1661,7 +1657,7 @@
       </c>
       <c r="V7" s="34" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="W7" s="34" t="inlineStr"/>
@@ -1883,7 +1879,7 @@
       </c>
       <c r="V9" s="34" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="W9" s="34" t="inlineStr"/>
@@ -2462,7 +2458,7 @@
       </c>
       <c r="V14" s="50" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="W14" s="50" t="inlineStr"/>
@@ -3609,11 +3605,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W24" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W24" s="50" t="inlineStr"/>
       <c r="X24" s="50" t="inlineStr">
         <is>
           <t>Yellow</t>
@@ -3728,11 +3720,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W25" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W25" s="34" t="inlineStr"/>
       <c r="X25" s="34" t="inlineStr">
         <is>
           <t>Yellow</t>
@@ -3847,11 +3835,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W26" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W26" s="50" t="inlineStr"/>
       <c r="X26" s="50" t="inlineStr">
         <is>
           <t>Yellow</t>

--- a/docs/harness/wirelist/CAN-wirelist.xlsx
+++ b/docs/harness/wirelist/CAN-wirelist.xlsx
@@ -3916,7 +3916,7 @@
       </c>
       <c r="M27" s="29" t="inlineStr">
         <is>
-          <t>Ground point IF, I/P brace RH (EWD ground point IF, p.42)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="N27" s="28" t="inlineStr"/>
@@ -3925,7 +3925,11 @@
           <t>Cluster ground</t>
         </is>
       </c>
-      <c r="P27" s="29" t="inlineStr"/>
+      <c r="P27" s="29" t="inlineStr">
+        <is>
+          <t>M8 ring lug on the POWER box battery-negative bar (R213 / R217: a CAN node never on chassis); runs with the CAN trunk to the ECU, then with the ECU harness to the glove box</t>
+        </is>
+      </c>
       <c r="Q27" s="30" t="inlineStr">
         <is>
           <t>GND.t_cluster_gnd</t>
@@ -3933,7 +3937,7 @@
       </c>
       <c r="R27" s="31" t="inlineStr">
         <is>
-          <t>Chassis GND (Ground point IF, I/P brace RH (EWD ground point IF, p.42))</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
       <c r="S27" s="32" t="inlineStr"/>
@@ -3953,7 +3957,7 @@
         </is>
       </c>
       <c r="Y27" s="34" t="n">
-        <v>1320</v>
+        <v>1600</v>
       </c>
       <c r="Z27" s="35" t="inlineStr"/>
       <c r="AA27" s="36" t="inlineStr"/>
@@ -3970,7 +3974,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG27" s="38" t="inlineStr"/>
+      <c r="AG27" s="38" t="inlineStr">
+        <is>
+          <t>est length to the glove-box NEG bar (was factory ground point IF)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="39" t="inlineStr">
@@ -4023,7 +4031,7 @@
       </c>
       <c r="M28" s="45" t="inlineStr">
         <is>
-          <t>Ground point IF, I/P brace RH (EWD ground point IF, p.42)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="N28" s="44" t="inlineStr"/>
@@ -4032,7 +4040,11 @@
           <t>RealDash Pi ground</t>
         </is>
       </c>
-      <c r="P28" s="45" t="inlineStr"/>
+      <c r="P28" s="45" t="inlineStr">
+        <is>
+          <t>M8 ring lug on the POWER box battery-negative bar (R213 / R217: a CAN node never on chassis); runs with the CAN trunk to the ECU, then with the ECU harness to the glove box</t>
+        </is>
+      </c>
       <c r="Q28" s="46" t="inlineStr">
         <is>
           <t>GND.t_cluster_gnd</t>
@@ -4040,7 +4052,7 @@
       </c>
       <c r="R28" s="47" t="inlineStr">
         <is>
-          <t>Chassis GND (Ground point IF, I/P brace RH (EWD ground point IF, p.42))</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
       <c r="S28" s="48" t="inlineStr"/>
@@ -4060,7 +4072,7 @@
         </is>
       </c>
       <c r="Y28" s="50" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="Z28" s="51" t="inlineStr"/>
       <c r="AA28" s="52" t="inlineStr"/>
@@ -4077,7 +4089,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG28" s="54" t="inlineStr"/>
+      <c r="AG28" s="54" t="inlineStr">
+        <is>
+          <t>est length to the glove-box NEG bar (was factory ground point IF)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr"/>
